--- a/data/trans_orig/P1_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P1_R-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares unipersonales en 2007</t>
+          <t>Hogares unipersonales en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>27955</t>
+          <t>26977</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>52232</t>
+          <t>52085</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>37339</t>
+          <t>37578</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>64391</t>
+          <t>63793</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>71822</t>
+          <t>70628</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>106864</t>
+          <t>108586</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,86%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>641780</t>
+          <t>641927</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>666057</t>
+          <t>667035</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>92,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>623960</t>
+          <t>624558</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>651012</t>
+          <t>650773</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1275499</t>
+          <t>1273777</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1310541</t>
+          <t>1311735</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,89%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>42052</t>
+          <t>41154</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>73184</t>
+          <t>70217</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>61697</t>
+          <t>60996</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>93760</t>
+          <t>95183</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>110363</t>
+          <t>109059</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>157184</t>
+          <t>155084</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,03%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>888616</t>
+          <t>891583</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>919748</t>
+          <t>920646</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>92,7%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>874633</t>
+          <t>873210</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>906696</t>
+          <t>907397</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,32%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1773009</t>
+          <t>1775109</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1819830</t>
+          <t>1821134</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,35%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>37083</t>
+          <t>37817</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>67431</t>
+          <t>67647</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>57458</t>
+          <t>54964</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>89025</t>
+          <t>87910</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>103081</t>
+          <t>101101</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>147861</t>
+          <t>145894</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,71%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>611078</t>
+          <t>610862</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>641426</t>
+          <t>640692</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>90,03%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>594816</t>
+          <t>595931</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>626383</t>
+          <t>628877</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,98%</t>
+          <t>87,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1214489</t>
+          <t>1216456</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1259269</t>
+          <t>1261249</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>89,29%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,58%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>74297</t>
+          <t>76397</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>111748</t>
+          <t>112590</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>82020</t>
+          <t>80188</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>120244</t>
+          <t>119234</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>167774</t>
+          <t>165315</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>220284</t>
+          <t>220678</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,14%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>830474</t>
+          <t>829632</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>867925</t>
+          <t>865825</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>88,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>91,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>918368</t>
+          <t>919378</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>956592</t>
+          <t>958424</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>88,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1760550</t>
+          <t>1760156</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1813060</t>
+          <t>1815519</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>88,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,65%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>209536</t>
+          <t>208080</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>267820</t>
+          <t>268121</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>263461</t>
+          <t>264324</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>331569</t>
+          <t>329422</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>489298</t>
+          <t>494099</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>577801</t>
+          <t>579992</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,71%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3008723</t>
+          <t>3008422</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3067007</t>
+          <t>3068463</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>91,82%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3047628</t>
+          <t>3049775</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3115736</t>
+          <t>3114873</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>90,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6077940</t>
+          <t>6075749</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6166443</t>
+          <t>6161642</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,58%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares unipersonales en 2012</t>
+          <t>Hogares unipersonales en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>44024</t>
+          <t>45384</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>73554</t>
+          <t>75703</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>55703</t>
+          <t>56386</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>87437</t>
+          <t>88760</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>109584</t>
+          <t>107390</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>153042</t>
+          <t>150011</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>10,71%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>629915</t>
+          <t>627766</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>659445</t>
+          <t>658085</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,54%</t>
+          <t>89,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>609613</t>
+          <t>608290</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>641347</t>
+          <t>640664</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,46%</t>
+          <t>87,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>91,91%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1247477</t>
+          <t>1250508</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1290935</t>
+          <t>1293129</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,07%</t>
+          <t>89,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,33%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>59686</t>
+          <t>59626</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>95569</t>
+          <t>95419</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3043,7 +3043,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>61090</t>
+          <t>60409</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>93976</t>
+          <t>94236</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>128732</t>
+          <t>127066</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>175649</t>
+          <t>175689</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>922378</t>
+          <t>922528</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>958261</t>
+          <t>958321</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>90,63%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>938208</t>
+          <t>937948</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>971094</t>
+          <t>971775</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,9%</t>
+          <t>90,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1874482</t>
+          <t>1874442</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1921399</t>
+          <t>1923065</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,8%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>46012</t>
+          <t>48121</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>79888</t>
+          <t>81028</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>53149</t>
+          <t>52181</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>87330</t>
+          <t>85600</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>107178</t>
+          <t>106476</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>154852</t>
+          <t>154280</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,05%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>677735</t>
+          <t>676595</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>711611</t>
+          <t>709502</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,46%</t>
+          <t>89,31%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>689844</t>
+          <t>691574</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>724025</t>
+          <t>724993</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>88,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1379945</t>
+          <t>1380517</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1427619</t>
+          <t>1428321</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>93,06%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>74507</t>
+          <t>72868</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>112736</t>
+          <t>111691</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>116149</t>
+          <t>116983</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>163779</t>
+          <t>162957</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>200265</t>
+          <t>200453</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>260802</t>
+          <t>257767</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3799,7 +3799,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>12,89%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>835003</t>
+          <t>836048</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>873232</t>
+          <t>874871</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,1%</t>
+          <t>88,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>92,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>888122</t>
+          <t>888944</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>935752</t>
+          <t>934918</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,43%</t>
+          <t>84,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,96%</t>
+          <t>88,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1738838</t>
+          <t>1741873</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1799375</t>
+          <t>1799187</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,96%</t>
+          <t>87,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>252379</t>
+          <t>252517</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>322286</t>
+          <t>323157</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>316856</t>
+          <t>319615</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>391205</t>
+          <t>393320</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>591395</t>
+          <t>592116</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>689537</t>
+          <t>694341</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,94%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3104493</t>
+          <t>3103622</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3174400</t>
+          <t>3174262</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,63%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3167104</t>
+          <t>3164989</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3241453</t>
+          <t>3238694</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>88,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6295551</t>
+          <t>6290747</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6393693</t>
+          <t>6392972</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>90,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,52%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares unipersonales en 2016</t>
+          <t>Hogares unipersonales en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>66332</t>
+          <t>67432</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>101775</t>
+          <t>103280</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>65510</t>
+          <t>65895</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>99530</t>
+          <t>98352</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>143025</t>
+          <t>143542</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>191580</t>
+          <t>193800</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,38%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>573025</t>
+          <t>571520</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>608468</t>
+          <t>607368</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>84,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>90,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>573309</t>
+          <t>574487</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>607329</t>
+          <t>606944</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,21%</t>
+          <t>85,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,26%</t>
+          <t>90,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1156059</t>
+          <t>1153839</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1204614</t>
+          <t>1204097</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,78%</t>
+          <t>85,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,39%</t>
+          <t>89,35%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>88623</t>
+          <t>89150</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>128816</t>
+          <t>128606</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>83040</t>
+          <t>83870</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>125062</t>
+          <t>126589</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>179757</t>
+          <t>181576</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>240740</t>
+          <t>239747</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,61%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>893615</t>
+          <t>893825</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>933808</t>
+          <t>933281</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>87,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>91,28%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>917851</t>
+          <t>916324</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>959873</t>
+          <t>959043</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>87,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1824604</t>
+          <t>1825597</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1885587</t>
+          <t>1883768</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>91,21%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>78899</t>
+          <t>81926</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>118811</t>
+          <t>121322</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>79406</t>
+          <t>77937</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>119439</t>
+          <t>114944</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>170958</t>
+          <t>168881</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>224012</t>
+          <t>222981</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,44%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>640741</t>
+          <t>638230</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>680653</t>
+          <t>677626</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,36%</t>
+          <t>84,03%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>665572</t>
+          <t>670067</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>705605</t>
+          <t>707074</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,79%</t>
+          <t>85,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1320551</t>
+          <t>1321582</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1373605</t>
+          <t>1375682</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>85,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,93%</t>
+          <t>89,07%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>116328</t>
+          <t>116629</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>160704</t>
+          <t>160940</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>161589</t>
+          <t>159248</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>215009</t>
+          <t>213255</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>293032</t>
+          <t>290402</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>362230</t>
+          <t>359358</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,14%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>776863</t>
+          <t>776627</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>821239</t>
+          <t>820938</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,86%</t>
+          <t>82,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,59%</t>
+          <t>87,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>828770</t>
+          <t>830524</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>882190</t>
+          <t>884531</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,4%</t>
+          <t>79,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,52%</t>
+          <t>84,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1619116</t>
+          <t>1621988</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1688314</t>
+          <t>1690944</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,72%</t>
+          <t>81,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,21%</t>
+          <t>85,34%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>391908</t>
+          <t>385915</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>467061</t>
+          <t>462648</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>422524</t>
+          <t>426087</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>510518</t>
+          <t>512579</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>834114</t>
+          <t>834380</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>953145</t>
+          <t>950192</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,69%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2927289</t>
+          <t>2931702</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3002442</t>
+          <t>3008435</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,24%</t>
+          <t>86,37%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>88,63%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3034024</t>
+          <t>3031963</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3122018</t>
+          <t>3118455</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>85,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>87,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5985747</t>
+          <t>5988700</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6104778</t>
+          <t>6104512</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,7 +6197,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,26%</t>
+          <t>86,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares unipersonales en 2023</t>
+          <t>Hogares unipersonales en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>138404</t>
+          <t>137852</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>183900</t>
+          <t>181854</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>107488</t>
+          <t>107733</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>155432</t>
+          <t>155353</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>255797</t>
+          <t>256121</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>322985</t>
+          <t>326125</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,97%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>451541</t>
+          <t>453587</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>497037</t>
+          <t>497589</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,06%</t>
+          <t>71,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>78,22%</t>
+          <t>78,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>569898</t>
+          <t>569977</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>617842</t>
+          <t>617597</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>78,57%</t>
+          <t>78,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,18%</t>
+          <t>85,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1037787</t>
+          <t>1034647</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1104975</t>
+          <t>1104651</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>76,26%</t>
+          <t>76,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,2%</t>
+          <t>81,18%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>75975</t>
+          <t>70427</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>196280</t>
+          <t>195819</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>137019</t>
+          <t>137081</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>170471</t>
+          <t>169779</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>200588</t>
+          <t>191279</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>352085</t>
+          <t>349874</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,26%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>996584</t>
+          <t>997045</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1116889</t>
+          <t>1122437</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,55%</t>
+          <t>83,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>788180</t>
+          <t>788872</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>821632</t>
+          <t>821570</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,22%</t>
+          <t>82,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,71%</t>
+          <t>85,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1799431</t>
+          <t>1801642</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1950928</t>
+          <t>1960237</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,64%</t>
+          <t>83,74%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>91,11%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>95342</t>
+          <t>93941</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>133353</t>
+          <t>134278</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>52209</t>
+          <t>48355</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>133861</t>
+          <t>131433</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>139194</t>
+          <t>142303</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>250512</t>
+          <t>253091</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,45%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>571327</t>
+          <t>570402</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>609338</t>
+          <t>610739</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>81,08%</t>
+          <t>80,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>86,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>799505</t>
+          <t>801933</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>881157</t>
+          <t>885011</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,66%</t>
+          <t>85,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1387534</t>
+          <t>1384955</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1498852</t>
+          <t>1495743</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,71%</t>
+          <t>84,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>91,31%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>136013</t>
+          <t>136725</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>186765</t>
+          <t>184708</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>172059</t>
+          <t>172540</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>240521</t>
+          <t>243340</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>326724</t>
+          <t>329331</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>411097</t>
+          <t>411766</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,37%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>740066</t>
+          <t>742123</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>790818</t>
+          <t>790106</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,85%</t>
+          <t>80,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,32%</t>
+          <t>85,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>854411</t>
+          <t>851592</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>922873</t>
+          <t>922392</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,03%</t>
+          <t>77,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,29%</t>
+          <t>84,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1610666</t>
+          <t>1609997</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1695039</t>
+          <t>1692432</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,67%</t>
+          <t>79,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,84%</t>
+          <t>83,71%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>446849</t>
+          <t>465285</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>643924</t>
+          <t>645945</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>488579</t>
+          <t>493102</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>659073</t>
+          <t>660438</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1025000</t>
+          <t>1029354</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1279680</t>
+          <t>1279637</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,7 +8031,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2815893</t>
+          <t>2813872</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3012968</t>
+          <t>2994532</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>81,39%</t>
+          <t>81,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>87,08%</t>
+          <t>86,55%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3053207</t>
+          <t>3051842</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3223701</t>
+          <t>3219178</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,25%</t>
+          <t>82,21%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>86,84%</t>
+          <t>86,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5892417</t>
+          <t>5892460</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6147097</t>
+          <t>6142743</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8149,7 +8149,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,71%</t>
+          <t>85,65%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P1_R-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>26977</t>
+          <t>27856</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>52085</t>
+          <t>50971</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>37578</t>
+          <t>37756</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>63793</t>
+          <t>64686</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>70628</t>
+          <t>71007</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>108586</t>
+          <t>106000</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,67%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>641927</t>
+          <t>643041</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>667035</t>
+          <t>666156</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>624558</t>
+          <t>623665</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>650773</t>
+          <t>650595</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>90,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1273777</t>
+          <t>1276363</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1311735</t>
+          <t>1311356</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,86%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>41154</t>
+          <t>42712</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>70217</t>
+          <t>70506</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>60996</t>
+          <t>60051</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>95183</t>
+          <t>93962</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>109059</t>
+          <t>112014</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>155084</t>
+          <t>156470</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,11%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>891583</t>
+          <t>891294</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>920646</t>
+          <t>919088</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>873210</t>
+          <t>874431</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>907397</t>
+          <t>908342</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>90,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1775109</t>
+          <t>1773723</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1821134</t>
+          <t>1818179</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>91,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,2%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>37817</t>
+          <t>38108</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>67647</t>
+          <t>69386</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>54964</t>
+          <t>56116</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>87910</t>
+          <t>87285</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>101101</t>
+          <t>102684</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>145894</t>
+          <t>147661</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,84%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>610862</t>
+          <t>609123</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>640692</t>
+          <t>640401</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>89,77%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>595931</t>
+          <t>596556</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>628877</t>
+          <t>627725</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,14%</t>
+          <t>87,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>91,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1216456</t>
+          <t>1214689</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1261249</t>
+          <t>1259666</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>89,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,46%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>76397</t>
+          <t>76398</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>112590</t>
+          <t>112138</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>80188</t>
+          <t>80171</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>119234</t>
+          <t>120569</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>165315</t>
+          <t>166712</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>220678</t>
+          <t>222065</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,21%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>829632</t>
+          <t>830084</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>865825</t>
+          <t>865824</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,05%</t>
+          <t>88,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>919378</t>
+          <t>918043</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>958424</t>
+          <t>958441</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,52%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1760156</t>
+          <t>1758769</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1815519</t>
+          <t>1814122</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>88,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>91,58%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>208080</t>
+          <t>209412</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>268121</t>
+          <t>271884</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>264324</t>
+          <t>261588</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>329422</t>
+          <t>329584</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>494099</t>
+          <t>489979</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>579992</t>
+          <t>582606</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,75%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3008422</t>
+          <t>3004659</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3068463</t>
+          <t>3067131</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3049775</t>
+          <t>3049613</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3114873</t>
+          <t>3117609</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6075749</t>
+          <t>6073135</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6161642</t>
+          <t>6165762</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>91,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,64%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>45384</t>
+          <t>44169</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>75703</t>
+          <t>73635</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>56386</t>
+          <t>58054</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>88760</t>
+          <t>89446</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>107390</t>
+          <t>109007</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>150011</t>
+          <t>152552</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,89%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>627766</t>
+          <t>629834</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>658085</t>
+          <t>659300</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,24%</t>
+          <t>89,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>608290</t>
+          <t>607604</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>640664</t>
+          <t>638996</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>87,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1250508</t>
+          <t>1247967</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1293129</t>
+          <t>1291512</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>89,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,22%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>59626</t>
+          <t>58992</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>95419</t>
+          <t>94636</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>60409</t>
+          <t>59060</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>94236</t>
+          <t>95410</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>127066</t>
+          <t>129632</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>175689</t>
+          <t>175910</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,58%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>922528</t>
+          <t>923311</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>958321</t>
+          <t>958955</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,63%</t>
+          <t>90,7%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>937948</t>
+          <t>936774</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>971775</t>
+          <t>973124</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1874442</t>
+          <t>1874221</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1923065</t>
+          <t>1920499</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>91,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,68%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>48121</t>
+          <t>46340</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>81028</t>
+          <t>78833</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>52181</t>
+          <t>52820</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>85600</t>
+          <t>86054</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>106476</t>
+          <t>108231</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>154280</t>
+          <t>154712</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,08%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>676595</t>
+          <t>678790</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>709502</t>
+          <t>711283</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>89,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>691574</t>
+          <t>691120</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>724993</t>
+          <t>724354</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,99%</t>
+          <t>88,93%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1380517</t>
+          <t>1380085</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1428321</t>
+          <t>1426566</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>89,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>92,95%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>72868</t>
+          <t>70604</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>111691</t>
+          <t>109046</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>116983</t>
+          <t>117746</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>162957</t>
+          <t>161295</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>200453</t>
+          <t>205170</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>257767</t>
+          <t>262970</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>13,15%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>836048</t>
+          <t>838693</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>874871</t>
+          <t>877135</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,21%</t>
+          <t>88,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>888944</t>
+          <t>890606</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>934918</t>
+          <t>934155</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,51%</t>
+          <t>84,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>88,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1741873</t>
+          <t>1736670</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1799187</t>
+          <t>1794470</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,11%</t>
+          <t>86,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>89,74%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>252517</t>
+          <t>255201</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>323157</t>
+          <t>322954</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>319615</t>
+          <t>318571</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>393320</t>
+          <t>393250</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>592116</t>
+          <t>595702</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>694341</t>
+          <t>691765</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,9%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3103622</t>
+          <t>3103825</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3174262</t>
+          <t>3171578</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>90,58%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3164989</t>
+          <t>3165059</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3238694</t>
+          <t>3239738</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4220,7 +4220,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>91,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6290747</t>
+          <t>6293323</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6392972</t>
+          <t>6389386</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>90,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>91,47%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>67432</t>
+          <t>68128</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>103280</t>
+          <t>102229</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>65895</t>
+          <t>65374</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>98352</t>
+          <t>99959</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>143542</t>
+          <t>143155</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>193800</t>
+          <t>190326</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,12%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>571520</t>
+          <t>572571</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>607368</t>
+          <t>606672</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,69%</t>
+          <t>84,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>89,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>574487</t>
+          <t>572880</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>606944</t>
+          <t>607465</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,38%</t>
+          <t>85,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>90,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1153839</t>
+          <t>1157313</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1204097</t>
+          <t>1204484</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,62%</t>
+          <t>85,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,35%</t>
+          <t>89,38%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>89150</t>
+          <t>89344</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>128606</t>
+          <t>128277</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>83870</t>
+          <t>85117</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>126589</t>
+          <t>126294</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>181576</t>
+          <t>181844</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>239747</t>
+          <t>241397</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,69%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>893825</t>
+          <t>894154</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>933281</t>
+          <t>933087</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,42%</t>
+          <t>87,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>916324</t>
+          <t>916619</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>959043</t>
+          <t>957796</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>87,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1825597</t>
+          <t>1823947</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1883768</t>
+          <t>1883500</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
+          <t>88,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>91,2%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>81926</t>
+          <t>80769</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>121322</t>
+          <t>117977</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>77937</t>
+          <t>80308</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>114944</t>
+          <t>117497</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>168881</t>
+          <t>167945</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>222981</t>
+          <t>224755</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,55%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>638230</t>
+          <t>641575</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>677626</t>
+          <t>678783</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,03%</t>
+          <t>84,47%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>89,37%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>670067</t>
+          <t>667514</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>707074</t>
+          <t>704703</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,36%</t>
+          <t>85,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>89,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1321582</t>
+          <t>1319808</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1375682</t>
+          <t>1376618</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,56%</t>
+          <t>85,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,07%</t>
+          <t>89,13%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>116629</t>
+          <t>117959</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>160940</t>
+          <t>162033</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>159248</t>
+          <t>161326</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>213255</t>
+          <t>214209</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>290402</t>
+          <t>292817</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>359358</t>
+          <t>358898</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>18,11%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>776627</t>
+          <t>775534</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>820938</t>
+          <t>819608</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,83%</t>
+          <t>82,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,56%</t>
+          <t>87,42%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>830524</t>
+          <t>829570</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>884531</t>
+          <t>882453</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,57%</t>
+          <t>79,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,74%</t>
+          <t>84,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1621988</t>
+          <t>1622448</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1690944</t>
+          <t>1688529</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,86%</t>
+          <t>81,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,34%</t>
+          <t>85,22%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>385915</t>
+          <t>385870</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>462648</t>
+          <t>468053</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6019,7 +6019,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>426087</t>
+          <t>426715</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>512579</t>
+          <t>512088</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>834380</t>
+          <t>832352</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>950192</t>
+          <t>950207</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,7 +6084,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2931702</t>
+          <t>2926297</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3008435</t>
+          <t>3008480</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,7 +6127,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,37%</t>
+          <t>86,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3031963</t>
+          <t>3032454</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3118455</t>
+          <t>3117827</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,54%</t>
+          <t>85,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>87,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5988700</t>
+          <t>5988685</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6104512</t>
+          <t>6106540</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6202,7 +6202,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>88,0%</t>
         </is>
       </c>
     </row>
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>158762</t>
+          <t>170635</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>137852</t>
+          <t>147097</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>181854</t>
+          <t>196937</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>28,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>136807</t>
+          <t>145812</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>107733</t>
+          <t>128806</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>155353</t>
+          <t>163705</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>22,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>295569</t>
+          <t>316446</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>256121</t>
+          <t>288175</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>326125</t>
+          <t>343515</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>24,11%</t>
         </is>
       </c>
     </row>
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>476679</t>
+          <t>520075</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>453587</t>
+          <t>493773</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>497589</t>
+          <t>543613</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>75,02%</t>
+          <t>75,3%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,38%</t>
+          <t>71,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>78,31%</t>
+          <t>78,7%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>588523</t>
+          <t>588368</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>569977</t>
+          <t>570475</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>617597</t>
+          <t>605374</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>81,14%</t>
+          <t>80,14%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>78,58%</t>
+          <t>77,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,15%</t>
+          <t>82,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1065203</t>
+          <t>1108443</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1034647</t>
+          <t>1081374</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1104651</t>
+          <t>1136714</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>78,28%</t>
+          <t>77,79%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>76,03%</t>
+          <t>75,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,18%</t>
+          <t>79,78%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>148129</t>
+          <t>173990</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>70427</t>
+          <t>150993</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>195819</t>
+          <t>201336</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>152892</t>
+          <t>168262</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>137081</t>
+          <t>150246</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>169779</t>
+          <t>188223</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>301021</t>
+          <t>342252</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>191279</t>
+          <t>311264</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>349874</t>
+          <t>375265</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>17,7%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1044735</t>
+          <t>874927</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>997045</t>
+          <t>847581</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1122437</t>
+          <t>897924</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>87,58%</t>
+          <t>83,41%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,58%</t>
+          <t>80,81%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>85,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>805759</t>
+          <t>903212</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>788872</t>
+          <t>883251</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>821570</t>
+          <t>921228</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>84,05%</t>
+          <t>84,3%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,29%</t>
+          <t>82,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,7%</t>
+          <t>85,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1850495</t>
+          <t>1778139</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1801642</t>
+          <t>1745126</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1960237</t>
+          <t>1809127</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>83,86%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,74%</t>
+          <t>82,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>85,32%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>113387</t>
+          <t>136560</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>93941</t>
+          <t>113614</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>134278</t>
+          <t>162108</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>97784</t>
+          <t>111402</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>48355</t>
+          <t>94861</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>131433</t>
+          <t>128858</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>211172</t>
+          <t>247962</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>142303</t>
+          <t>217411</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>253091</t>
+          <t>278111</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>17,22%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>591293</t>
+          <t>666513</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>570402</t>
+          <t>640965</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>610739</t>
+          <t>689459</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>83,91%</t>
+          <t>83,0%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>80,94%</t>
+          <t>79,81%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,67%</t>
+          <t>85,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>835582</t>
+          <t>700857</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>801933</t>
+          <t>683401</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>885011</t>
+          <t>717398</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>89,52%</t>
+          <t>86,28%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,92%</t>
+          <t>84,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>88,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1426874</t>
+          <t>1367370</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1384955</t>
+          <t>1337221</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1495743</t>
+          <t>1397921</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>87,11%</t>
+          <t>84,65%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,55%</t>
+          <t>82,78%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>86,54%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>159113</t>
+          <t>169792</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>136725</t>
+          <t>147051</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>184708</t>
+          <t>194907</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>215027</t>
+          <t>232058</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>172540</t>
+          <t>210770</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>243340</t>
+          <t>256634</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>374140</t>
+          <t>401850</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>329331</t>
+          <t>371131</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>411766</t>
+          <t>436378</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,69%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>767718</t>
+          <t>820270</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>742123</t>
+          <t>795155</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>790106</t>
+          <t>843011</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>82,83%</t>
+          <t>82,85%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,07%</t>
+          <t>80,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>85,15%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>879905</t>
+          <t>886983</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>851592</t>
+          <t>862407</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>922392</t>
+          <t>908271</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>80,36%</t>
+          <t>79,26%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,78%</t>
+          <t>77,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>81,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1647623</t>
+          <t>1707254</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1609997</t>
+          <t>1672726</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1692432</t>
+          <t>1737973</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>81,49%</t>
+          <t>80,95%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,63%</t>
+          <t>79,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,71%</t>
+          <t>82,4%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>579391</t>
+          <t>650977</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>465285</t>
+          <t>601919</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>645945</t>
+          <t>699677</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>602510</t>
+          <t>657534</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>493102</t>
+          <t>618777</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>660438</t>
+          <t>694281</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1181902</t>
+          <t>1308510</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1029354</t>
+          <t>1249391</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1279637</t>
+          <t>1369989</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>18,85%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2880426</t>
+          <t>2881785</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2813872</t>
+          <t>2833085</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2994532</t>
+          <t>2930843</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>83,25%</t>
+          <t>81,57%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>81,33%</t>
+          <t>80,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>86,55%</t>
+          <t>82,96%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3109770</t>
+          <t>3079420</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3051842</t>
+          <t>3042673</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3219178</t>
+          <t>3118177</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>83,77%</t>
+          <t>82,4%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,21%</t>
+          <t>81,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>86,72%</t>
+          <t>83,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>5990195</t>
+          <t>5961206</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5892460</t>
+          <t>5899727</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6142743</t>
+          <t>6020325</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>83,52%</t>
+          <t>82,0%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,16%</t>
+          <t>81,15%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,65%</t>
+          <t>82,81%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">

--- a/data/trans_orig/P1_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P1_R-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares unipersonales en 2007 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si conforma un hogar unipersonal en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares unipersonales en 2012 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si conforma un hogar unipersonal en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares unipersonales en 2016 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si conforma un hogar unipersonal en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares unipersonales en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si conforma un hogar unipersonal en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
